--- a/notebooks/매핑 골든셋 ord 추가.xlsx
+++ b/notebooks/매핑 골든셋 ord 추가.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="KOSIS_매핑" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J90"/>
+  <dimension ref="A1:J86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,39 +471,57 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A021-01</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+          <t>A001-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>DT_1B040A3</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>101</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>국가데이터처(주민등록인구현황)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>9,384,325명 (2024.1)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1B040A3</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>매칭 실패</t>
+          <t>값 확인됨 (일치)</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>관세청 '1~20일 수출입 현황'은 월 2회 발표되는 잠정치(가집계)로 KOSIS에 정식 등재되지 않음. 관세청 수출입무역통계(또는 무역통계정보포털) 원자료 직접 확인 필요</t>
+          <t>서울특별시 총인구, 2024.1=9,384,325명. 기사 수치(9,384,000명)와 사실상 일치(연간 값이 아니라 2024년 초 시점 월간값으로 확인됨). 2024년 12월 기준으로는 9,331,828명으로 더 낮아짐(연중 계속 감소)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Claude(코시스 커넥터 검색, 매칭 실패)</t>
+          <t>Claude(코시스 API 직접 조회, 수치 확인)</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A021-02</t>
+          <t>A001-01(중복)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -513,29 +531,29 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>매칭 실패</t>
+          <t>해당없음 (수치 주장 없음)</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>상동 (반도체 21.8%, 관세청 잠정치)</t>
+          <t>원본 골든셋에 claim_id 'A001-01'이 article_id 'A001'로 중복 기재되어 있으나 claim_sentence가 없고, article_title도 다른 기사('배스킨라빈스... 핑크드림가든')로 되어 있음 - 추출 파이프라인 오류로 추정, 원본 확인 필요</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Claude(코시스 커넥터 검색, 매칭 실패)</t>
+          <t>Claude(원본에 claim 없음, 매칭 대상 아님)</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A021-03</t>
+          <t>A002-01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -545,987 +563,775 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>매칭 실패</t>
+          <t>해당없음 (수치 주장 없음)</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>상동 (자동차 9.2%, 관세청 잠정치)</t>
+          <t>"매우 훌륭하다"... 트럼프 손녀 카이 트럼프도 엄지 척한 K푸드 - claim_sentence 없음, 통계 주장 없는 기사</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Claude(코시스 커넥터 검색, 매칭 실패)</t>
+          <t>Claude(원본에 claim 없음, 매칭 대상 아님)</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A022-01</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>DT_1K41013</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>101</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>국가데이터처(서비스업동향조사)</t>
-        </is>
-      </c>
+          <t>A003-01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1K41013</t>
-        </is>
-      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>표 후보 확인 (총계 항목 미확인)</t>
+          <t>매칭 실패</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>국가데이터처 서비스업동향조사 '소매업태별 판매액지수'. 조회 결과 백화점/대형마트 등 업태별 지수만 제공, 전체 합계(총지수) 행이 안 보여 -2.2% 총계와 직접 대조 못함 - 상품군별 표(DT_1K41012) 등 재확인 필요</t>
+          <t>더본코리아 상장 첫날 종가(51,400원, 공모가 대비 +51.18%) - 개별 종목 주가는 한국거래소 시세 데이터로 KOSIS(국가승인통계) 대상이 아님. KRX 정보데이터시스템에서 직접 확인 필요</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Claude(코시스 커넥터 자동 매칭, 수치 미대조)</t>
+          <t>Claude(코시스 커넥터 검색, 매칭 실패)</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A022-02</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>DT_1DA7E33S</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>101</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>국가데이터처(경제활동인구조사)</t>
-        </is>
-      </c>
+          <t>A003-02</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1DA7E33S</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>표 후보 확인 (최신월 미제공)</t>
+          <t>매칭 실패</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>경제활동인구조사 '행정구역(시도)/산업별 취업자'(objL1=00 전국, objL2=41 건설업). 조회 시점 기준 최신 데이터가 2024.12(201.07만명)까지만 제공되어 기사의 2025.1월(192.1만명)과 직접 대조 못함 - 시차 있는 최신치 재조회 필요</t>
+          <t>더본코리아 5/2 종가(26,950원) - 상동 사유</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Claude(코시스 커넥터 자동 매칭, 수치 미대조)</t>
+          <t>Claude(코시스 커넥터 검색, 매칭 실패)</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A022-03</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+          <t>A004-01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>DT_1B04006</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>101</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>국가데이터처(주민등록인구현황)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>5,392,237명 (2025.4, 0~14세 합계)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1B04006</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>매칭 실패</t>
+          <t>값 확인됨 (참고용)</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>관세청 '2월 1~20일 수출' 잠정치, KOSIS 미등재 (A021과 동일 사유)</t>
+          <t>전국 0~14세 인구를 1세 단위로 합산한 값. 기사는 구체적 수치 없이 '역대 최저치'라고만 서술 - 실제로 최저치인지는 전체 시계열을 다 비교해야 확정되므로 참고용으로 표기</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Claude(코시스 커넥터 검색, 매칭 실패)</t>
+          <t>Claude(코시스 API 직접 조회, 수치 확인)</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A023-01</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>DT_1J22112</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>101</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>국가데이터처(소비자물가조사)</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>116.29(지수)/+2.1%</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1J22112</t>
-        </is>
-      </c>
+          <t>A005-01</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>값 확인됨 (일치)</t>
+          <t>해당없음 (수치 주장 없음)</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2025.3 총지수 116.29, 2024.3(113.95) 대비 +2.05%. 기사 수치와 정확히 일치</t>
+          <t>롯데월드 피카츄 퍼레이드 - claim_sentence 없음, 통계 주장 없는 기사</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Claude(코시스 API 직접 조회, 수치 확인)</t>
+          <t>Claude(원본에 claim 없음, 매칭 대상 아님)</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A023-02</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>DT_1J22112</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>101</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>국가데이터처(소비자물가조사)</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>123.19(지수)/+3.6%</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1J22112</t>
-        </is>
-      </c>
+          <t>A006-01</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>값 확인됨 (일치)</t>
+          <t>해당없음 (수치 주장 없음)</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>가공식품 지수 2025.3=123.19, 2024.3(118.92) 대비 +3.59%. 기사 수치(3.6%)와 정확히 일치</t>
+          <t>최태원 회장 SKT 해킹 사과 - claim_sentence 없음, 통계 주장 없는 기사</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Claude(코시스 API 직접 조회, 수치 확인)</t>
+          <t>Claude(원본에 claim 없음, 매칭 대상 아님)</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A023-03</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>DT_1J22112</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>101</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>국가데이터처(소비자물가조사)</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>123.8(지수)/+3.0%</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1J22112</t>
-        </is>
-      </c>
+          <t>A007-01</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>값 확인됨 (일치)</t>
+          <t>해당없음 (수치 주장 없음)</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>외식 지수 2025.3=123.8, 2024.3(120.21) 대비 +2.99%. 기사 수치(3%)와 정확히 일치</t>
+          <t>귀가 중 여성 강제추행 40대 2심서 무죄 - claim_sentence 없음, 통계 주장 없는 기사</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Claude(코시스 API 직접 조회, 수치 확인)</t>
+          <t>Claude(원본에 claim 없음, 매칭 대상 아님)</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A024-01</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>DT_1B8000G</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>101</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>국가데이터처(인구동향조사)</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>20,083명</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1B8000G</t>
-        </is>
-      </c>
+          <t>A008-01</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>값 확인됨 (불일치)</t>
+          <t>매칭 실패</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>KOSIS 2024.11 전국 출생아수=20,083명. 기사 수치(20,095명)와 12명 차이 - 잠정치/확정치 개편 차이로 추정, 원문 확인 필요</t>
+          <t>스트레스 DSR 금리 0.38%(2024.2 도입) - 금융위원회·금융감독원의 가계부채 관리 정책(규제 비율)으로, KOSIS에 등재되는 조사 통계가 아님</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Claude(코시스 API 직접 조회, 수치 확인)</t>
+          <t>Claude(코시스 커넥터 검색, 매칭 실패)</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A024-02</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>DT_1B8000G</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>101</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>국가데이터처(인구동향조사)</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>220,061명</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1B8000G</t>
-        </is>
-      </c>
+          <t>A009-01</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>값 확인됨 (불일치)</t>
+          <t>매칭 실패</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2024년 1~11월 월별 출생아수를 합산한 결과 220,061명. 기사 수치(220,094명)와 33명 차이 - A024-01/A025-01/A025-03와 동일하게 소폭 개정 차이로 추정</t>
+          <t>미국의 수입차 관세 25% - 미국 정부의 관세 정책 수치로 KOSIS(국내 통계) 대상 아님</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Claude(코시스 API 직접 조회, 수치 확인)</t>
+          <t>Claude(코시스 커넥터 검색, 매칭 실패)</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A024-03</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>DT_1B8000G</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>101</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>국가데이터처(인구동향조사)</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>18,581건</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1B8000G</t>
-        </is>
-      </c>
+          <t>A010-01</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>값 확인됨 (일치)</t>
+          <t>해당없음 (수치 주장 없음)</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2024.11 혼인건수=18,581건. 기사 수치와 정확히 일치</t>
+          <t>김범석 직무대행 F4 회의 - claim_sentence 없음, 통계 주장 없는 기사</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Claude(코시스 API 직접 조회, 수치 확인)</t>
+          <t>Claude(원본에 claim 없음, 매칭 대상 아님)</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A025-01</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>DT_1B8000G</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>101</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>국가데이터처(인구동향조사)</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>222,412건</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1B8000G</t>
-        </is>
-      </c>
+          <t>A011-01</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>값 확인됨 (불일치)</t>
+          <t>해당없음 (수치 주장 없음)</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2024년 연간 혼인건수=222,412건. 기사 수치(222,422건)와 10건 차이 - 확정치 개편 가능성, 확인 필요</t>
+          <t>직무에 충실한 공직자 외부서 흔들어선 안돼 - claim_sentence 없음, 통계 주장 없는 기사</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Claude(코시스 API 직접 조회, 수치 확인)</t>
+          <t>Claude(원본에 claim 없음, 매칭 대상 아님)</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A025-02</t>
+          <t>A012-01</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DT_1B8000G</t>
+          <t>DT_127003_001</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>101</v>
+        <v>127</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>국가데이터처(인구동향조사)</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>22,519건</t>
-        </is>
-      </c>
+          <t>과학기술정보통신부(국가연구개발사업통계)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1B8000G</t>
+          <t>https://kosis.kr/statHtml/statHtml.do?orgId=127&amp;tblId=DT_127003_001</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>값 확인됨 (일치)</t>
+          <t>표 후보 확인 (항목 없음)</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2024.12 혼인건수=22,519건. 기사 수치와 정확히 일치</t>
+          <t>국가연구개발사업의 총괄 집행 추이 표를 확인했으나 예산·집행액·사업수·과제수만 제공하고 '성공률' 항목 자체가 없음. 성공률은 KISTEP '국가연구개발사업 성과분석' 등 별도 자료일 가능성 - 추가 확인 필요</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Claude(코시스 API 직접 조회, 수치 확인)</t>
+          <t>Claude(코시스 커넥터 자동 매칭, 수치 미대조/불일치)</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A025-03</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>DT_1B8000G</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>101</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>국가데이터처(인구동향조사)</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>91,151건</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1B8000G</t>
-        </is>
-      </c>
+          <t>A013-01</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>값 확인됨 (불일치)</t>
+          <t>매칭 실패</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2024년 연간 이혼건수=91,151건. 기사 수치(91,155건)와 4건 차이</t>
+          <t>AI 관련 R&amp;D 예산 1조2000억원(정부 R&amp;D의 약 4%) - 연구개발활동조사(DT_KBA0010) 등에서 'AI 분야'로 별도 분류된 예산 항목을 찾지 못함. 기재부/과기정통부의 R&amp;D 예산 배분안 자료로 추정, KOSIS 미등재 가능성 높음</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Claude(코시스 API 직접 조회, 수치 확인)</t>
+          <t>Claude(코시스 커넥터 검색, 매칭 실패)</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A026-01</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>DT_1L9U001</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>101</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>국가데이터처(가계동향조사)</t>
-        </is>
-      </c>
+          <t>A014-01</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1L9U001</t>
-        </is>
-      </c>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>표 후보 확인 (주기 확인 필요)</t>
+          <t>해당없음 (수치 주장 없음)</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>가계동향조사 '가구당 월평균 가계수지'(분기). 2025.1분기 535만1000원 미대조</t>
+          <t>이재명, 경제5단체 간담회 - claim_sentence 없음, 통계 주장 없는 기사</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Claude(코시스 커넥터 자동 매칭, 수치 미대조)</t>
+          <t>Claude(원본에 claim 없음, 매칭 대상 아님)</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A026-02</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>DT_1L9U001</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>101</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>국가데이터처(가계동향조사)</t>
-        </is>
-      </c>
+          <t>A015-01</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1L9U001</t>
-        </is>
-      </c>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>표 후보 확인 (주기 확인 필요)</t>
+          <t>매칭 실패</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>소득 1분위 가구 소득(114만원) - 10분위/5분위 별도 분류표 필요, 미대조</t>
+          <t>영국산 자동차 관세 27.5%→10% 인하 - 미국의 대(對)영국 관세 정책 수치로 KOSIS 대상 아님</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Claude(코시스 커넥터 자동 매칭, 수치 미대조)</t>
+          <t>Claude(코시스 커넥터 검색, 매칭 실패)</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A026-03</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>DT_1HDALF05</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>101</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>국가데이터처(가계금융복지조사)</t>
-        </is>
-      </c>
+          <t>A015-02</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1HDALF05</t>
-        </is>
-      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>표 후보 확인 (주기 불일치 가능)</t>
+          <t>매칭 실패</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>'소득분배지표'는 가계금융복지조사(연간) 기반 - 기사의 분기 5분위배율(6.32배)과 조사 주기가 다를 수 있어 별도 분기 가계동향조사 표 확인 필요</t>
+          <t>미국 자동차 수입량 802만대/빅3 221만대(28%) - 미국 시장 데이터(컨설팅업체 글로벌데이터 인용)로 국내 KOSIS 통계 대상 아님</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Claude(코시스 커넥터 자동 매칭, 수치 미대조)</t>
+          <t>Claude(코시스 커넥터 검색, 매칭 실패)</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A027-01</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>DT_1J22112</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>101</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>국가데이터처(소비자물가조사)</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>116.27(지수)/+1.9%</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1J22112</t>
-        </is>
-      </c>
+          <t>A015-03</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>값 확인됨 (일치)</t>
+          <t>매칭 실패</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2025.5 총지수 116.27, 2024.5(114.1) 대비 +1.90%. 기사 수치와 정확히 일치</t>
+          <t>영국의 대미 자동차 수출 64억파운드 - 영국 무역 통계로 KOSIS 대상 아님</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Claude(코시스 API 직접 조회, 수치 확인)</t>
+          <t>Claude(코시스 커넥터 검색, 매칭 실패)</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A027-02</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>DT_1J22112</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>101</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>국가데이터처(소비자물가조사)</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>축산물121.52/돼지고기125.73/쇠고기104.65/계란139.36 (2025.5)</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1J22112</t>
-        </is>
-      </c>
+          <t>A016-01</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>값 확인됨 (일치)</t>
+          <t>해당없음 (수치 주장 없음)</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>축산물 +6.19%→6.2%, 돼지고기 +8.43%→8.4%, 국산쇠고기 +5.28%→5.3%, 달걀 +3.76%→3.8% (모두 2024.5 대비). 기사의 4개 수치 전부 정확히 일치</t>
+          <t>전통시장 84곳서 수산물 온누리상품권 환급 - claim_sentence 없음, 통계 주장 없는 기사</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Claude(코시스 API 직접 조회, 수치 확인)</t>
+          <t>Claude(원본에 claim 없음, 매칭 대상 아님)</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A027-03</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>DT_1J22005</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>101</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>국가데이터처(소비자물가조사)</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>119.2(지수)/+2.3%</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1J22005</t>
-        </is>
-      </c>
+          <t>A017-01</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>값 확인됨 (일치)</t>
+          <t>해당없음 (수치 주장 없음)</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>생활물가지수, 2025.5=119.2, 2024.5(116.53) 대비 +2.29%→+2.3%. 기사 수치와 정확히 일치</t>
+          <t>KDI 구조개혁 안하면 2041년부터 마이너스 성장 - claim_sentence 없음, 통계 주장 없는 기사</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Claude(코시스 API 직접 조회, 수치 확인)</t>
+          <t>Claude(원본에 claim 없음, 매칭 대상 아님)</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A028-01</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
+          <t>A018-01</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>DT_343_2010_S0016</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>343</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>한국거래소(증권·파생상품시장통계)</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>https://kosis.kr/statHtml/statHtml.do?orgId=343&amp;tblId=DT_343_2010_S0016</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>매칭 실패</t>
+          <t>표 후보 확인 (분류 불일치)</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>'국민 삶의 질' 보고서의 3개년 평균 삶의만족도(6.06점, OECD 33위, 0~10점 척도)는 KOSIS 검색으로 후보 표(INH_1SSSP020R '삶의 만족도')를 찾았으나 해당 표는 만족/불만족 응답비율(%) 형태라 점수(6.06점) 형식과 불일치 - 별도 산출 지표로 KOSIS 내 직접 매칭 어려움</t>
+          <t>방산·조선 시가총액 상위 10종목 합계(129조원) - KOSIS 표는 '산업별'(예: 제조업, 금융업 등 대분류) 시가총액만 제공하고, 기사처럼 '상위 10종목'을 직접 골라 합산한 수치는 표에 없음. 언론사 자체 집계로 추정</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Claude(코시스 커넥터 검색, 매칭 실패)</t>
+          <t>Claude(코시스 커넥터 자동 매칭, 수치 미대조/불일치)</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A028-02</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
+          <t>A018-02</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>DT_343_2010_S0016</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>343</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>한국거래소(증권·파생상품시장통계)</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>https://kosis.kr/statHtml/statHtml.do?orgId=343&amp;tblId=DT_343_2010_S0016</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>매칭 실패</t>
+          <t>표 후보 확인 (분류 불일치)</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2023년 삶의만족도 6.4점 - 상동 사유</t>
+          <t>자동차 업종 상위 10종목 시가총액(109조원) - 상동 사유</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Claude(코시스 커넥터 검색, 매칭 실패)</t>
+          <t>Claude(코시스 커넥터 자동 매칭, 수치 미대조/불일치)</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A029-01</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
+          <t>A018-03</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>DT_343_2010_S0016</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>343</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>한국거래소(증권·파생상품시장통계)</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>https://kosis.kr/statHtml/statHtml.do?orgId=343&amp;tblId=DT_343_2010_S0016</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>매칭 실패</t>
+          <t>표 후보 확인 (분류 불일치)</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1980~1984년생 코호트별 학력 비율은 인구총조사 마이크로데이터를 이용한 자체 분석 수치로 추정되며, KOSIS의 표준 정기표에서 동일한 출생연도 코호트 분류를 찾지 못함</t>
+          <t>작년말 방산·조선 시가총액(67조원) - 상동 사유</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Claude(코시스 커넥터 검색, 매칭 실패)</t>
+          <t>Claude(코시스 커넥터 자동 매칭, 수치 미대조/불일치)</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A029-02</t>
+          <t>A019-01</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -1535,29 +1341,29 @@
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>매칭 실패</t>
+          <t>해당없음 (수치 주장 없음)</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1990~1994년생 코호트 - 상동 사유</t>
+          <t>롯데손보, 900억대 후순위채 조기 상환 못해 - claim_sentence 없음, 통계 주장 없는 기사</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Claude(코시스 커넥터 검색, 매칭 실패)</t>
+          <t>Claude(원본에 claim 없음, 매칭 대상 아님)</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A030-01</t>
+          <t>A020-01</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -1567,29 +1373,29 @@
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>매칭 실패</t>
+          <t>해당없음 (수치 주장 없음)</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>기획재정부 '2025년 경제성장률 전망치(1.8%)'는 전망치(예측 수치)로 확정 통계가 아니므로 KOSIS 대상 아님</t>
+          <t>김문수 반명 빅텐트 대선 입장문 - claim_sentence 없음, 통계 주장 없는 기사</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Claude(코시스 커넥터 검색, 매칭 실패)</t>
+          <t>Claude(원본에 claim 없음, 매칭 대상 아님)</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A031-01</t>
+          <t>A021-01</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -1604,7 +1410,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>OECD 자체 집계 대도시/소도시 집값 비교 보고서 - KOSIS 국내 통계와 직접 매칭 어려움, 미탐색</t>
+          <t>관세청 '1~20일 수출입 현황'은 월 2회 발표되는 잠정치(가집계)로 KOSIS에 정식 등재되지 않음. 관세청 수출입무역통계(또는 무역통계정보포털) 원자료 직접 확인 필요 -&gt;직접확인하니 월별 통계는 존재하나 일별 통계는 확인할 수 없어 정확한 값 판단 불가</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1621,45 +1427,27 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A032-01</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>DT_1J22112</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>101</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>국가데이터처(소비자물가조사)</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>116.08(지수)/+2.0%</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1J22112</t>
-        </is>
-      </c>
+          <t>A021-02</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>값 확인됨 (일치)</t>
+          <t>매칭 실패</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2025.2 총지수 116.08. 기사 원문의 지수(116.08)와 정확히 일치</t>
+          <t>상동 (반도체 21.8%, 관세청 잠정치)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Claude(코시스 API 직접 조회, 수치 확인)</t>
+          <t>Claude(코시스 커넥터 검색, 매칭 실패)</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -1671,45 +1459,27 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A032-02</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>DT_1J22112</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>101</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>국가데이터처(소비자물가조사)</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>130.35(지수)/+6.3%</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1J22112</t>
-        </is>
-      </c>
+          <t>A021-03</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>값 확인됨 (일치)</t>
+          <t>매칭 실패</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>석유류 지수 2025.2=130.35, 2024.2(122.66) 대비 +6.27%. 기사 수치(6.3%)와 정확히 일치</t>
+          <t>상동 (자동차 9.2%, 관세청 잠정치)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Claude(코시스 API 직접 조회, 수치 확인)</t>
+          <t>Claude(코시스 커넥터 검색, 매칭 실패)</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -1721,27 +1491,41 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A032-03</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
+          <t>A022-01</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>DT_1K41013</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>101</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>국가데이터처(서비스업동향조사)</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1K41013</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>미완료</t>
+          <t>표 후보 확인 (총계 항목 미확인)</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>생활물가지수 2.6% - A027-03과 동일 사유로 별도 탐색 필요</t>
+          <t>국가데이터처 서비스업동향조사 '소매업태별 판매액지수'를 조회한 결과 '시도별 소매판매액지수'는 확인했으나 '전국'에 대한 통계는 없어 -2.2% 총계와 직접 대조 못함</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Claude(코시스 커넥터, 미탐색)</t>
+          <t>Claude(코시스 커넥터 자동 매칭, 수치 미대조)</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -1753,36 +1537,36 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A033-01</t>
+          <t>A022-02</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>DT_1R11001_FRM101</t>
+          <t>DT_1DA7E33S</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>360</v>
+        <v>101</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>한국무역협회(SITC에의한무역통계)</t>
+          <t>국가데이터처(경제활동인구조사)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://kosis.kr/statHtml/statHtml.do?orgId=360&amp;tblId=DT_1R11001_FRM101</t>
+          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1DA7E33S</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>표 후보 확인 (정의 차이 주의)</t>
+          <t>표 후보 확인 (최신월 미제공)</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>한국무역협회 SITC 무역통계(월간, 품목별). 기사의 산업부·관세청 연간 총수출액(6838억달러)과 집계기준이 다를 수 있어 대조 필요</t>
+          <t>경제활동인구조사 '행정구역(시도)/산업별 취업자'(objL1=00 전국, objL2=41 건설업). 조회 시점 기준 최신 데이터가 2024.12(201.07만명)까지만 제공되어 기사의 2025.1월(192.1만명)과 직접 대조 못함 - 시차 있는 최신치 재조회 필요</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1799,41 +1583,27 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A033-02</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>DT_1R11001_FRM101</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>360</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>한국무역협회(SITC에의한무역통계)</t>
-        </is>
-      </c>
+          <t>A022-03</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>https://kosis.kr/statHtml/statHtml.do?orgId=360&amp;tblId=DT_1R11001_FRM101</t>
-        </is>
-      </c>
+      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>표 후보 확인 (정의 차이 주의)</t>
+          <t>매칭 실패</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>무역수지(수입액,흑자규모) - 상동 사유로 미대조</t>
+          <t>관세청 '2월 1~20일 수출' 잠정치, KOSIS 미등재 (A021과 동일 사유)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Claude(코시스 커넥터 자동 매칭, 수치 미대조)</t>
+          <t>Claude(코시스 커넥터 검색, 매칭 실패)</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -1845,41 +1615,45 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A033-03</t>
+          <t>A023-01</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>DT_1R11001_FRM101</t>
+          <t>DT_1J22112</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>360</v>
+        <v>101</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>한국무역협회(SITC에의한무역통계)</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr"/>
+          <t>국가데이터처(소비자물가조사)</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>116.29(지수)/+2.1%</t>
+        </is>
+      </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://kosis.kr/statHtml/statHtml.do?orgId=360&amp;tblId=DT_1R11001_FRM101</t>
+          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1J22112</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>표 후보 확인 (정의 차이 주의)</t>
+          <t>값 확인됨 (일치)</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2024.12 수출액(613.8억달러) - 상동</t>
+          <t>2025.3 총지수 116.29, 2024.3(113.95) 대비 +2.05%. 기사 수치와 일치</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Claude(코시스 커넥터 자동 매칭, 수치 미대조)</t>
+          <t>Claude(코시스 API 직접 조회, 수치 확인)</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -1891,41 +1665,45 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A033-04</t>
+          <t>A023-02</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>DT_1R11001_FRM101</t>
+          <t>DT_1J22112</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>360</v>
+        <v>101</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>한국무역협회(SITC에의한무역통계)</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
+          <t>국가데이터처(소비자물가조사)</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>123.19(지수)/+3.6%</t>
+        </is>
+      </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://kosis.kr/statHtml/statHtml.do?orgId=360&amp;tblId=DT_1R11001_FRM101</t>
+          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1J22112</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>표 후보 확인 (정의 차이 주의)</t>
+          <t>값 확인됨 (일치)</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2024.12 반도체 수출 증가율(31.5%) - SITC 776 코드로 조회 가능하나 미대조</t>
+          <t>가공식품 지수 2025.3=123.19, 2024.3(118.92) 대비 +3.59%. 기사 수치(3.6%)와 일치</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Claude(코시스 커넥터 자동 매칭, 수치 미대조)</t>
+          <t>Claude(코시스 API 직접 조회, 수치 확인)</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -1937,12 +1715,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A034-01</t>
+          <t>A023-03</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>DT_1KE10041</t>
+          <t>DT_1J22112</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -1950,27 +1728,27 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>국가데이터처(온라인쇼핑동향조사)</t>
+          <t>국가데이터처(소비자물가조사)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>21,942,389백만원/+2.6%</t>
+          <t>123.8(지수)/+3.0%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1KE10041</t>
+          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1J22112</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>값 확인됨 (유사, 완전일치 아님)</t>
+          <t>값 확인됨 (일치)</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2025.4 전체 거래액=21,942,389백만원(21조9424억원), 2024.4(21,383,534백만원) 대비 +2.61%. 기사의 증가율(2.5%)과는 근접하지만 절대액(21조6858억원)과는 약 2565억원 차이 - 상품+서비스 집계범위 차이 가능성, 원문 재확인 권장</t>
+          <t>외식 지수 2025.3=123.8, 2024.3(120.21) 대비 +2.99%. 기사 수치(3%)와 정확히 일치</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -1987,12 +1765,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A034-02</t>
+          <t>A024-01</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>DT_1KE10041</t>
+          <t>DT_1B8000G</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -2000,27 +1778,27 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>국가데이터처(온라인쇼핑동향조사)</t>
+          <t>국가데이터처(인구동향조사)</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>208,720백만원/-12.6%</t>
+          <t>20,083명</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1KE10041</t>
+          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1B8000G</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>값 확인됨 (근접, 불일치)</t>
+          <t>값 확인됨 (불일치)</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>가방 2025.4=208,720백만원, 2024.4(238,750백만원) 대비 -12.58%. 기사 수치(-11.3%)와 1.3%p 차이 - 근접하나 정확히 일치하지 않음</t>
+          <t>KOSIS 2024.11 전국 출생아수=20,083명. 기사 수치(20,095명)와 12명 차이 - 잠정치/확정치 개편 차이로 추정</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2037,12 +1815,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A034-03</t>
+          <t>A024-02</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>DT_1KE10041</t>
+          <t>DT_1B8000G</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -2050,27 +1828,27 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>국가데이터처(온라인쇼핑동향조사)</t>
+          <t>국가데이터처(인구동향조사)</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>446,594백만원/-49.0%</t>
+          <t>220,061명</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1KE10041</t>
+          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1B8000G</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>값 확인됨 (일치)</t>
+          <t>값 확인됨 (불일치)</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>이쿠폰서비스 2025.4=446,594백만원, 2024.4(876,287백만원) 대비 -49.03%. 기사 수치(-49.1%)와 사실상 일치</t>
+          <t>2024년 1~11월 월별 출생아수를 합산한 결과 220,061명. 기사 수치(220,094명)와 33명 차이 - A024-01/A025-01/A025-03와 동일하게 개정 차이로 추정</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2087,12 +1865,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A035-01</t>
+          <t>A024-03</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>DT_1DA7E33S</t>
+          <t>DT_1B8000G</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -2100,28 +1878,32 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>국가데이터처(경제활동인구조사)</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
+          <t>국가데이터처(인구동향조사)</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>18,581건</t>
+        </is>
+      </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1DA7E33S</t>
+          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1B8000G</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>표 후보 확인 (세부 코드 미확인)</t>
+          <t>값 확인됨 (일치)</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>경제활동인구조사 산업별 취업자 표는 확인했으나, '보건업 및 사회복지서비스업' 세부 objL2 코드를 아직 특정하지 못함 (제조업=10, 건설업=41은 확인됨)</t>
+          <t>2024.11 혼인건수=18,581건. 기사 수치와 일치</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Claude(코시스 커넥터 자동 매칭, 수치 미대조)</t>
+          <t>Claude(코시스 API 직접 조회, 수치 확인)</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2133,12 +1915,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A035-02</t>
+          <t>A025-01</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>DT_1DA7E33S</t>
+          <t>DT_1B8000G</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -2146,28 +1928,32 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>국가데이터처(경제활동인구조사)</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
+          <t>국가데이터처(인구동향조사)</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>222,412건</t>
+        </is>
+      </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1DA7E33S</t>
+          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1B8000G</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>표 후보 확인 (세부 코드 미확인)</t>
+          <t>값 확인됨 (불일치)</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2014→2024 보건복지 종사자 증가 - 상동 사유</t>
+          <t>2024년 연간 혼인건수=222,412건. 기사 수치(222,422건)와 10건 차이 - 확정치 개편 가능성</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Claude(코시스 커넥터 자동 매칭, 수치 미대조)</t>
+          <t>Claude(코시스 API 직접 조회, 수치 확인)</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2179,12 +1965,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A035-03</t>
+          <t>A025-02</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>DT_1DA7E33S</t>
+          <t>DT_1B8000G</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -2192,32 +1978,32 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>국가데이터처(경제활동인구조사)</t>
+          <t>국가데이터처(인구동향조사)</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>4,455천명(2024)/4,458.6천명(2014)</t>
+          <t>22,519건</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1DA7E33S</t>
+          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1B8000G</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>표 후보 확인 (비율 계산 필요)</t>
+          <t>값 확인됨 (일치)</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>제조업(objL2=10) 취업자수는 확보했으나 전체 취업자 대비 비율(17%→15.6%) 계산은 분모(전체 취업자수) 대입 후 재계산 필요</t>
+          <t>2024.12 혼인건수=22,519건. 기사 수치와 일치</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Claude(코시스 커넥터 자동 매칭, 수치 미대조)</t>
+          <t>Claude(코시스 API 직접 조회, 수치 확인)</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2229,27 +2015,45 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A036-01</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr"/>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
+          <t>A025-03</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>DT_1B8000G</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>101</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>국가데이터처(인구동향조사)</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>91,151건</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1B8000G</t>
+        </is>
+      </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>매칭 실패</t>
+          <t>값 확인됨 (불일치)</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>전국 주택 시가총액(6839조원) - KOSIS 로컬/전체 검색에서 '주택시가총액' 표를 찾지 못함. 한국부동산원이 별도 발표하는 자료로 추정, KOSIS 미등재 가능성 높음</t>
+          <t>2024년 연간 이혼건수=91,151건. 기사 수치(91,155건)와 4건 차이</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Claude(코시스 커넥터 검색, 매칭 실패)</t>
+          <t>Claude(코시스 API 직접 조회, 수치 확인)</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2261,27 +2065,41 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A036-02</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr"/>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
+          <t>A026-01</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>DT_1L9U001</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>101</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>국가데이터처(가계동향조사)</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1L9U001</t>
+        </is>
+      </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>매칭 실패</t>
+          <t>표 후보 확인 (해당 주기 미제공)</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>수도권 비중(67.7%) - 상동</t>
+          <t>가계동향조사 '가구당 월평균 가계수지'(분기). 기사 수치는 2025.1분기 (535만1000원)이지만 kosis데이터는 2024.4분기까지만 제공됨.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Claude(코시스 커넥터 검색, 매칭 실패)</t>
+          <t>Claude(코시스 커넥터 자동 매칭, 수치 미대조)</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2293,27 +2111,41 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A036-03</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr"/>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
+          <t>A026-02</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>DT_1L9U001</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>101</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>국가데이터처(가계동향조사)</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1L9U001</t>
+        </is>
+      </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>매칭 실패</t>
+          <t>표 후보 확인 (해당 주기 미제공)</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>유형별 비중(아파트76.3% 등) - 상동</t>
+          <t>상동 이유</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Claude(코시스 커넥터 검색, 매칭 실패)</t>
+          <t>Claude(코시스 커넥터 자동 매칭, 수치 미대조)</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -2325,27 +2157,41 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A037-01</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr"/>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
+          <t>A026-03</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>DT_1HDALF05</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>101</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>국가데이터처(가계금융복지조사)</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1HDALF05</t>
+        </is>
+      </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>매칭 실패</t>
+          <t>표 후보 확인 (해당 주기 미제공)</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>대한상의 자체 설문(기업 AI 도입률 6.4%) - KOSIS 로컬 카탈로그에서 매칭 표 없음, 확인 결과 민간기관(대한상공회의소) 자체조사로 KOSIS 미등재</t>
+          <t>상동 이유</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Claude(코시스 커넥터 검색, 매칭 실패)</t>
+          <t>Claude(코시스 커넥터 자동 매칭, 수치 미대조)</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2357,27 +2203,45 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A037-02</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr"/>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
+          <t>A027-01</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>DT_1J22112</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>101</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>국가데이터처(소비자물가조사)</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>116.27(지수)/+1.9%</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1J22112</t>
+        </is>
+      </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>매칭 실패</t>
+          <t>값 확인됨 (일치)</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>산업별 AI도입률(정보통신업26%,제조업4%) - 상동</t>
+          <t>2025.5 총지수 116.27, 2024.5(114.1) 대비 +1.90%. 기사 수치와 일치</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Claude(코시스 커넥터 검색, 매칭 실패)</t>
+          <t>Claude(코시스 API 직접 조회, 수치 확인)</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -2389,12 +2253,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A038-01</t>
+          <t>A027-02</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>DT_1DA7001S</t>
+          <t>DT_1J22112</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -2402,17 +2266,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>국가데이터처(경제활동인구조사)</t>
+          <t>국가데이터처(소비자물가조사)</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>28,041,100명</t>
+          <t>축산물121.52/돼지고기125.73/쇠고기104.65/계란139.36 (2025.5)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1DA7001S</t>
+          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1J22112</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2422,7 +2286,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>성별 경제활동인구총괄, 2024.12 전국 취업자=28,041.1천명. 기사 수치(28,041,000명)와 사실상 일치(반올림 차이)</t>
+          <t>축산물 +6.19%→6.2%, 돼지고기 +8.43%→8.4%, 국산쇠고기 +5.28%→5.3%, 달걀 +3.76%→3.8% (모두 2024.5 대비). 기사의 4개 수치 전부 일치</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2439,12 +2303,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A038-02</t>
+          <t>A027-03</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>DT_1DA7002S</t>
+          <t>DT_1J22005</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -2452,17 +2316,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>국가데이터처(경제활동인구조사)</t>
+          <t>국가데이터처(소비자물가조사)</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>119.2(지수)/+2.3%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1DA7002S</t>
+          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1J22005</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2472,7 +2336,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>연령별 경제활동인구총괄, 15-29세(청년) 2024.12 실업률=5.9%. 기사 수치와 정확히 일치</t>
+          <t>생활물가지수, 2025.5=119.2, 2024.5(116.53) 대비 +2.29%→+2.3%. 기사 수치와 일치</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2489,45 +2353,27 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A038-03</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>DT_1DA7001S</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>101</v>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>국가데이터처(경제활동인구조사)</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>61.4%</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1DA7001S</t>
-        </is>
-      </c>
+          <t>A028-01</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>값 확인됨 (일치)</t>
+          <t>매칭 실패</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2024.12 전국 고용률=61.4%. 기사 수치와 정확히 일치</t>
+          <t>'국민 삶의 질' 보고서의 3개년 평균 삶의만족도(6.06점, OECD 33위, 0~10점 척도)는 KOSIS 검색으로 후보 표(INH_1SSSP020R '삶의 만족도')를 찾았으나 해당 표는 만족/불만족 응답비율(%) 형태라 점수(6.06점) 형식과 불일치 - 별도 산출 지표로 KOSIS 내 직접 매칭 어려움</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Claude(코시스 API 직접 조회, 수치 확인)</t>
+          <t>Claude(코시스 커넥터 검색, 매칭 실패)</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -2539,41 +2385,27 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A039-01</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>DT_1C91</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>101</v>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>국가데이터처(지역소득)</t>
-        </is>
-      </c>
+          <t>A028-02</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1C91</t>
-        </is>
-      </c>
+      <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>표 후보 확인 (주기 불일치)</t>
+          <t>매칭 실패</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>지역소득, 시도별 경제활동별 지역내총생산 - 조회해보니 연간 데이터만 제공(2019~2024), 분기 데이터 없음. 기사의 2025.1분기 전기대비 0.1% 증가는 별도 분기 지표(예: 분기 지역경제동향, 속보성)일 가능성 - 추가 탐색 필요</t>
+          <t>2023년 삶의만족도 6.4점 - 상동 이유</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Claude(코시스 커넥터 자동 매칭, 수치 미대조)</t>
+          <t>Claude(코시스 커넥터 검색, 매칭 실패)</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -2585,41 +2417,27 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A039-02</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>DT_1C91</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>101</v>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>국가데이터처(지역소득)</t>
-        </is>
-      </c>
+          <t>A029-01</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1C91</t>
-        </is>
-      </c>
+      <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>표 후보 확인 (주기 불일치)</t>
+          <t>매칭 실패</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>경북1.6%/울산1.4%/서울1.0% - 상동 사유로 분기 데이터 확인 안됨</t>
+          <t>1980~1984년생 코호트별 학력 비율은 인구총조사 마이크로데이터를 이용한 자체 분석 수치로 추정되며, KOSIS의 표준 정기표에서 동일한 출생연도 코호트 분류를 찾지 못함</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Claude(코시스 커넥터 자동 매칭, 수치 미대조)</t>
+          <t>Claude(코시스 커넥터 검색, 매칭 실패)</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -2631,41 +2449,27 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A039-03</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>DT_1C91</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>101</v>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>국가데이터처(지역소득)</t>
-        </is>
-      </c>
+          <t>A029-02</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1C91</t>
-        </is>
-      </c>
+      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>표 후보 확인 (주기 불일치)</t>
+          <t>매칭 실패</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>건설업 GRDP -12.4%(분기) - 상동</t>
+          <t>1990~1994년생 코호트 - 상동 이유</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Claude(코시스 커넥터 자동 매칭, 수치 미대조)</t>
+          <t>Claude(코시스 커넥터 검색, 매칭 실패)</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -2677,7 +2481,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A040-01</t>
+          <t>A030-01</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -2692,7 +2496,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>청년층 '쉬었음' 인구(50.4만명) - 경제활동인구조사 내 '활동상태별 비경제활동인구'(쉬었음/가사/심신장애 등) 세부표를 로컬 카탈로그에서 찾지 못함, 별도 특수 분류표로 추정</t>
+          <t>기획재정부 '2025년 경제성장률 전망치(1.8%)'는 전망치(예측 수치)로 확정 통계가 아니므로 KOSIS 대상 아님</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2709,45 +2513,27 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A040-02</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>DT_1DA7002S</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>101</v>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>국가데이터처(경제활동인구조사)</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>44.3%</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1DA7002S</t>
-        </is>
-      </c>
+          <t>A031-01</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>값 확인됨 (일치)</t>
+          <t>매칭 실패</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>연령별 경제활동인구총괄, 15-29세 2025.2 고용률=44.3%. 기사 수치와 정확히 일치</t>
+          <t>OECD 자체 집계 대도시/소도시 집값 비교 보고서 - KOSIS 국내 통계와 직접 매칭 어려움</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Claude(코시스 API 직접 조회, 수치 확인)</t>
+          <t>Claude(코시스 커넥터 검색, 매칭 실패)</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -2759,12 +2545,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A040-03</t>
+          <t>A032-01</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>DT_1DA7002S</t>
+          <t>DT_1J22112</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -2772,17 +2558,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>국가데이터처(경제활동인구조사)</t>
+          <t>국가데이터처(소비자물가조사)</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>3,557,200명</t>
+          <t>116.08(지수)/+2.0%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1DA7002S</t>
+          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1J22112</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2792,7 +2578,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>15-29세 2025.2 취업자=3,557.2천명. 기사 수치(3,557,000명)와 사실상 일치(반올림 차이)</t>
+          <t>2025.2 총지수 116.08. 기사 원문의 지수(116.08)와 일치</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2809,27 +2595,45 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A041-01</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr"/>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
+          <t>A032-02</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>DT_1J22112</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>101</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>국가데이터처(소비자물가조사)</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>130.35(지수)/+6.3%</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1J22112</t>
+        </is>
+      </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>매칭 실패</t>
+          <t>값 확인됨 (일치)</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>가계금융복지조사 은퇴가구 최소/적정 생활비(원 단위) - '노후준비' 관련 검색 결과 모두 민간·타부처 패널조사(장애인삶패널, 다문화가족실태조사 등)만 나오고 통계청 가계금융복지조사 내 해당 항목 표는 찾지 못함</t>
+          <t>석유류 지수 2025.2=130.35, 2024.2(122.66) 대비 +6.27%. 기사 수치(6.3%)와 일치</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Claude(코시스 커넥터 검색, 매칭 실패)</t>
+          <t>Claude(코시스 API 직접 조회, 수치 확인)</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -2841,7 +2645,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A041-02</t>
+          <t>A032-03</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -2851,17 +2655,17 @@
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>매칭 실패</t>
+          <t>미완료</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>생활비 여유/부족 응답비율 - 상동</t>
+          <t>생활물가지수 2.6% - A027-03과 동일 사유로 별도 탐색 필요</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Claude(코시스 커넥터 검색, 매칭 실패)</t>
+          <t>Claude(코시스 커넥터, 미탐색)</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -2873,36 +2677,36 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A042-01</t>
+          <t>A033-01</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>DT_1K41013</t>
+          <t>DT_1R11001_FRM101</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>101</v>
+        <v>360</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>국가데이터처(서비스업동향조사)</t>
+          <t>한국무역협회(SITC에의한무역통계)</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1K41013</t>
+          <t>https://kosis.kr/statHtml/statHtml.do?orgId=360&amp;tblId=DT_1R11001_FRM101</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>표 후보 확인 (총계 항목 미확인)</t>
+          <t>표 후보 확인 (정의 차이 주의)</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>A022-01과 동일 수치(2024년 연간 소매판매 -2.2%), 동일 표·동일 사유</t>
+          <t>한국무역협회 SITC 무역통계(월간, 품목별). 기사의 산업부·관세청 연간 총수출액(683,609,488천달러)과 유사한 값이나 기사 통계는 산업통상자원부와 관세청 기준이므로 기준이 다를 수 있음</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -2919,45 +2723,41 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A042-02</t>
+          <t>A033-02</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>DT_1JH20201</t>
+          <t>DT_1R11001_FRM101</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>101</v>
+        <v>360</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>국가데이터처(전산업생산지수)</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>113.5(2024)/111.7(2023)/+1.6%</t>
-        </is>
-      </c>
+          <t>한국무역협회(SITC에의한무역통계)</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1JH20201</t>
+          <t>https://kosis.kr/statHtml/statHtml.do?orgId=360&amp;tblId=DT_1R11001_FRM101</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>값 확인됨 (근접, 불일치)</t>
+          <t xml:space="preserve">값 확인됨(일치) </t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>전산업생산지수(원지수, 농림어업포함) 2024=113.5, 2023=111.7 대비 +1.61%. 기사 수치(+1.7%)와 0.1%p 차이 - 근접하나 정확히 일치하지 않음 (농림어업 제외 기준도 동일하게 +1.6%)</t>
+          <t>작년(2023년)수입액: 631,767,209천달러(단위만 다름) 수출액: 683,609,488천달러 확인. 따라서 흑자: 518억 달러 일치.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Claude(코시스 API 직접 조회, 수치 확인)</t>
+          <t>Claude(코시스 커넥터 자동 매칭, 수치 미대조)</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -2969,45 +2769,41 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A042-03</t>
+          <t>A033-03</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>DT_1G18011</t>
+          <t>DT_1R11001_FRM101</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>101</v>
+        <v>360</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>국가데이터처(건설경기동향조사)</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>136,209,903백만원/-4.6%</t>
-        </is>
-      </c>
+          <t>한국무역협회(SITC에의한무역통계)</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1G18011</t>
+          <t>https://kosis.kr/statHtml/statHtml.do?orgId=360&amp;tblId=DT_1R11001_FRM101</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>값 확인됨 (근접, 불일치)</t>
+          <t>값 확인됨(근접, 불일치)</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>건설기성액(불변) 2024=136,209,903백만원, 2023(142,775,612백만원) 대비 -4.60%. 기사 수치(-4.9%)와 0.3%p 차이 - 근접하나 정확히 일치하지 않음</t>
+          <t>2024.12 수출액:61,359,250천달러로 기사의 613.8억달러와 유사하나 약간의 차이가 있음.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Claude(코시스 API 직접 조회, 수치 확인)</t>
+          <t>Claude(코시스 커넥터 자동 매칭, 수치 미대조)</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -3019,100 +2815,108 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A043-01</t>
+          <t>A033-04</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>DT_1J22003</t>
+          <t>DT_1R11001_FRM101</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>101</v>
+        <v>360</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>통계청</t>
-        </is>
-      </c>
-      <c r="E61" t="n">
-        <v>116.38</v>
-      </c>
-      <c r="F61" t="inlineStr"/>
+          <t>한국무역협회(SITC에의한무역통계)</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>https://kosis.kr/statHtml/statHtml.do?orgId=360&amp;tblId=DT_1R11001_FRM101</t>
+        </is>
+      </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>값 확인됨(자동 API 검증)</t>
+          <t>매칭 실패</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>API 실측 116.38, 오차 0.00%. slots: period=202504,prd_se=M,region=전국</t>
+          <t>품목별 수출액, 수입액 표는 찾았으나 '반도체' 품목은 확인이 안됨.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Claude(Claude Code, KOSIS API 실측 검증)</t>
+          <t>Claude(코시스 커넥터 자동 매칭, 수치 미대조)</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A044-01</t>
+          <t>A034-01</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>DT_151Y001</t>
+          <t>DT_1KE10041</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>301</v>
+        <v>101</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>한국은행</t>
-        </is>
-      </c>
-      <c r="E62" t="n">
-        <v>1922706.5</v>
-      </c>
-      <c r="F62" t="inlineStr"/>
+          <t>국가데이터처(온라인쇼핑동향조사)</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>21,942,389백만원/+2.6%</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1KE10041</t>
+        </is>
+      </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>값 확인됨(자동 API 검증)</t>
+          <t>값 확인됨 (근접, 불일치)</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>API 실측 1,922,706.5십억원(=1922.7조원), 기사 1927.3조원 대비 오차 0.24%. slots: period=202404,account_item=가계신용</t>
+          <t>2025.4 전체 거래액=21,942,389백만원(21조9424억원), 2024.4(21,383,534백만원) 대비 +2.61%. 기사의 증가율(2.5%)과는 근접하지만 절대액(21조6858억원)과는 약 2565억원 차이 - 상품+서비스 집계범위 차이 가능성</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Claude(Claude Code, KOSIS API 실측 검증)</t>
+          <t>Claude(코시스 API 직접 조회, 수치 확인)</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A045-01</t>
+          <t>A034-02</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>DT_2KAA809</t>
+          <t>DT_1KE10041</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -3120,87 +2924,99 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>통계청</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
-        <v>415603.777</v>
-      </c>
-      <c r="F63" t="inlineStr"/>
+          <t>국가데이터처(온라인쇼핑동향조사)</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>208,720백만원/-12.6%</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1KE10041</t>
+        </is>
+      </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>값 확인됨(자동 API 검증)</t>
+          <t>값 확인됨 (근접, 불일치)</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>API 실측 415,603.777백만USD(=4156.0억달러), 오차 0.00%. slots: period=2024,country=대한민국</t>
+          <t>가방 2025.4=208,720백만원, 2024.4(238,750백만원) 대비 -12.58%. 기사 수치(-11.3%)와 1.3%p 차이 - 근접하나 정확히 일치하지 않음</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Claude(Claude Code, KOSIS API 실측 검증)</t>
+          <t>Claude(코시스 API 직접 조회, 수치 확인)</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A046-01</t>
+          <t>A034-03</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>TX_13301_A169</t>
+          <t>DT_1KE10041</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>133</v>
+        <v>101</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>국세청</t>
-        </is>
-      </c>
-      <c r="E64" t="n">
-        <v>1008282</v>
-      </c>
-      <c r="F64" t="inlineStr"/>
+          <t>국가데이터처(온라인쇼핑동향조사)</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>446,594백만원/-49.0%</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1KE10041</t>
+        </is>
+      </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>값 확인됨(자동 API 검증)</t>
+          <t>값 확인됨 (일치)</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>API 실측 1,008,282명, 오차 0.00%. slots: period=2024,taxpayer_type=합계,region_type=합계,reason=총계</t>
+          <t>이쿠폰서비스 2025.4=446,594백만원, 2024.4(876,287백만원) 대비 -49.03%. 기사 수치(-49.1%)와 사실상 일치</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Claude(Claude Code, KOSIS API 실측 검증)</t>
+          <t>Claude(코시스 API 직접 조회, 수치 확인)</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A047-01</t>
+          <t>A035-01</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>DT_104Y282</t>
+          <t>DT_1DA7E33S</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -3208,87 +3024,91 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>통계청</t>
-        </is>
-      </c>
-      <c r="E65" t="n">
-        <v>7138694.4</v>
-      </c>
-      <c r="F65" t="inlineStr"/>
+          <t>국가데이터처(경제활동인구조사)</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1DA7E33S</t>
+        </is>
+      </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>값 확인됨(자동 API 검증)</t>
+          <t>표 후보 확인 (세부 코드 미확인)</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>API 실측 7,138,694.4십억원(=7138.7조원), 기사 7158조원 대비 오차 0.27%. slots: period=2024,region=전국</t>
+          <t>경제활동인구조사 산업별 취업자 표는 확인했으나  '보건업 및 사회복지서비스업' 세부 objL2 코드를 아직 특정하지 못함 (제조업=10, 건설업=41은 확인됨)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Claude(Claude Code, KOSIS API 실측 검증)</t>
+          <t>Claude(코시스 커넥터 자동 매칭, 수치 미대조)</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A048-01</t>
+          <t>A035-02</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>DT_511Y002</t>
+          <t>DT_1DA7E33S</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>301</v>
+        <v>101</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>한국은행</t>
-        </is>
-      </c>
-      <c r="E66" t="n">
-        <v>87.90000000000001</v>
-      </c>
-      <c r="F66" t="inlineStr"/>
+          <t>국가데이터처(경제활동인구조사)</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1DA7E33S</t>
+        </is>
+      </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>값 확인됨(자동 API 검증)</t>
+          <t>표 후보 확인 (세부 코드 미확인)</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>API 실측 87.9, 기사 88.4 대비 오차 0.57%. slots: period=202412,csi_type=CCSI,csi_classification=전체</t>
+          <t>2014→2024 보건복지 종사자 증가 - 상동 이유</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Claude(Claude Code, KOSIS API 실측 검증)</t>
+          <t>Claude(코시스 커넥터 자동 매칭, 수치 미대조)</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A049-01</t>
+          <t>A035-03</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>DT_1C8015</t>
+          <t>DT_1DA7E33S</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -3296,351 +3116,309 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>통계청</t>
-        </is>
-      </c>
-      <c r="E67" t="n">
-        <v>99.40000000000001</v>
-      </c>
-      <c r="F67" t="inlineStr"/>
+          <t>국가데이터처(경제활동인구조사)</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>4,455천명(2024)/4,458.6천명(2014)</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1DA7E33S</t>
+        </is>
+      </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>값 확인됨(자동 API 검증)</t>
+          <t>표 후보 확인 (비율 계산 필요)</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>API 실측 99.4, 기사 98.5 대비 오차 0.91%. slots: period=202505,index_type=동행지수 순환변동치</t>
+          <t>제조업(objL2=10) 취업자수는 확보했으나 전체 취업자 대비 비율(17%→15.6%) 계산은 분모(전체 취업자수) 대입 후 재계산 필요</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Claude(Claude Code, KOSIS API 실측 검증)</t>
+          <t>Claude(코시스 커넥터 자동 매칭, 수치 미대조)</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A050-01</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>DT_102006_001</t>
-        </is>
-      </c>
-      <c r="C68" t="n">
-        <v>184</v>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>기획재정부</t>
-        </is>
-      </c>
-      <c r="E68" t="n">
-        <v>1175</v>
-      </c>
+          <t>A036-01</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr"/>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>값 확인됨(자동 API 검증)</t>
+          <t>매칭 실패</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>API 실측 1175.0조원, 기사 1175.2조원과 거의 일치. slots: period=2024,debt_item=국가채무</t>
+          <t>전국 주택 시가총액(6839조원) - KOSIS 로컬/전체 검색에서 '주택시가총액' 표를 찾지 못함. 한국부동산원이 별도 발표하는 자료로 추정, KOSIS 미등재 가능성 높음</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Claude(Claude Code, KOSIS API 실측 검증)</t>
+          <t>Claude(코시스 커넥터 검색, 매칭 실패)</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A050-02</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>DT_102N_AD01</t>
-        </is>
-      </c>
-      <c r="C69" t="n">
-        <v>184</v>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>기획재정부</t>
-        </is>
-      </c>
-      <c r="E69" t="n">
-        <v>-43521</v>
-      </c>
+          <t>A036-02</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>값 확인됨(자동 API 검증)</t>
+          <t>매칭 실패</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>API 실측 -43,521십억원(=-43.5조원), 오차 0.05%. slots: period=202412,balance_type=통합재정수지</t>
+          <t>수도권 비중(67.7%) - 상동</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Claude(Claude Code, KOSIS API 실측 검증)</t>
+          <t>Claude(코시스 커넥터 검색, 매칭 실패)</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A051-01</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>DT_32202_A100</t>
-        </is>
-      </c>
-      <c r="C70" t="n">
-        <v>322</v>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>국민연금공단</t>
-        </is>
-      </c>
-      <c r="E70" t="n">
-        <v>21984003</v>
-      </c>
+          <t>A036-03</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr"/>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>값 확인됨(자동 API 검증)</t>
+          <t>매칭 실패</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>API 실측(연말기준) 21,984,003명, 기사(10월말) 21,812,216명 대비 오차 0.79%(월 차이). slots: period=2024,region=전국,subscriber_type=전체,gender=계</t>
+          <t>유형별 비중(아파트76.3% 등) - 상동</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Claude(Claude Code, KOSIS API 실측 검증)</t>
+          <t>Claude(코시스 커넥터 검색, 매칭 실패)</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A051-02</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>DT_32202_B004</t>
-        </is>
-      </c>
-      <c r="C71" t="n">
-        <v>322</v>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>국민연금공단</t>
-        </is>
-      </c>
-      <c r="E71" t="n">
-        <v>7404430</v>
-      </c>
+          <t>A037-01</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr"/>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>값 확인됨(자동 API 검증)</t>
+          <t>매칭 실패</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>API 실측(연말기준) 7,404,430명, 기사(10월) 7,235,901명 대비 오차 2.33%(월 차이). slots: period=2024,benefit_type=전체,age=전체,gender=전체</t>
+          <t>대한상의 자체 설문(기업 AI 도입률 6.4%) - KOSIS 로컬 카탈로그에서 매칭 표 없음, 확인 결과 민간기관(대한상공회의소) 자체조사로 KOSIS 미등재</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Claude(Claude Code, KOSIS API 실측 검증)</t>
+          <t>Claude(코시스 커넥터 검색, 매칭 실패)</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A053-01</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>DT_401Y015</t>
-        </is>
-      </c>
-      <c r="C72" t="n">
-        <v>301</v>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>한국은행</t>
-        </is>
-      </c>
-      <c r="E72" t="n">
-        <v>141.98</v>
-      </c>
+          <t>A037-02</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>값 확인됨(자동 API 검증)</t>
+          <t>매칭 실패</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>API 실측 141.98, 오차 0.11%. slots: period=202412,item=총지수,currency_basis=원화기준</t>
+          <t>산업별 AI도입률(정보통신업26%,제조업4%) - 상동</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Claude(Claude Code, KOSIS API 실측 검증)</t>
+          <t>Claude(코시스 커넥터 검색, 매칭 실패)</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A053-02</t>
+          <t>A038-01</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>DT_402Y014</t>
+          <t>DT_1DA7001S</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>301</v>
+        <v>101</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>한국은행</t>
-        </is>
-      </c>
-      <c r="E73" t="n">
-        <v>133.56</v>
-      </c>
-      <c r="F73" t="inlineStr"/>
+          <t>국가데이터처(경제활동인구조사)</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>28,041,100명</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1DA7001S</t>
+        </is>
+      </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>값 확인됨(자동 API 검증)</t>
+          <t>값 확인됨 (일치)</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>API 실측 133.56, 오차 0.14%. slots: period=202412,item=총지수,currency_basis=원화기준</t>
+          <t>성별 경제활동인구총괄, 2024.12 전국 취업자=28,041.1천명. 기사 수치(28,041,000명)와 사실상 일치(반올림 차이)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Claude(Claude Code, KOSIS API 실측 검증)</t>
+          <t>Claude(코시스 API 직접 조회, 수치 확인)</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A054-01</t>
+          <t>A038-02</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>DT_512Y013</t>
+          <t>DT_1DA7002S</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>301</v>
+        <v>101</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>한국은행</t>
-        </is>
-      </c>
-      <c r="E74" t="n">
-        <v>86.40000000000001</v>
-      </c>
-      <c r="F74" t="inlineStr"/>
+          <t>국가데이터처(경제활동인구조사)</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>5.9%</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1DA7002S</t>
+        </is>
+      </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>값 확인됨(자동 API 검증)</t>
+          <t>값 확인됨 (일치)</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>API 실측 86.4, 오차 0.58%. slots: period=202501,industry=전산업,bsi_type=기업심리지수실적</t>
+          <t>연령별 경제활동인구총괄, 15-29세(청년) 2024.12 실업률=5.9%. 기사 수치와 일치</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Claude(Claude Code, KOSIS API 실측 검증)</t>
+          <t>Claude(코시스 API 직접 조회, 수치 확인)</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A055-01</t>
+          <t>A038-03</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>DT_1ED0001</t>
+          <t>DT_1DA7001S</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -3648,43 +3426,49 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>통계청</t>
-        </is>
-      </c>
-      <c r="E75" t="n">
-        <v>55.8</v>
-      </c>
-      <c r="F75" t="inlineStr"/>
+          <t>국가데이터처(경제활동인구조사)</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>61.4%</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1DA7001S</t>
+        </is>
+      </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>값 확인됨(자동 API 검증)</t>
+          <t>값 확인됨 (일치)</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>API 실측 55.8kg, 오차 0.00%. slots: period=2024,grain_type=쌀,use_type=계</t>
+          <t>2024.12 전국 고용률=61.4%. 기사 수치와 정확히 일치</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Claude(Claude Code, KOSIS API 실측 검증)</t>
+          <t>Claude(코시스 API 직접 조회, 수치 확인)</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A056-01</t>
+          <t>A039-01</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>DT_1B26001_A01</t>
+          <t>DT_1C91</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -3692,43 +3476,45 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>통계청</t>
-        </is>
-      </c>
-      <c r="E76" t="n">
-        <v>493599</v>
-      </c>
-      <c r="F76" t="inlineStr"/>
+          <t>국가데이터처(지역소득)</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1C91</t>
+        </is>
+      </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>값 확인됨(자동 API 검증)</t>
+          <t>표 후보 확인 (주기 불일치)</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>API 실측(월별, 실험적 prd_se=M) 493,599명, 오차 0.08%. slots: period=202509,prd_se=M,region=전국 — table_params.json 문서엔 연간만 확인돼 있었으나 월별도 정상 동작 확인됨</t>
+          <t>지역소득, 시도별 경제활동별 지역내총생산 - 조회해보니 연간 데이터만 제공(2019~2024), 분기 데이터 없음. 기사의 2025.1분기 전기대비 0.1% 증가는 별도 분기 지표(예: 분기 지역경제동향, 속보성)일 가능성 - 추가 탐색 필요</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Claude(Claude Code, KOSIS API 실측 검증)</t>
+          <t>Claude(코시스 커넥터 자동 매칭, 수치 미대조)</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A057-01</t>
+          <t>A039-02</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>DT_1TEC_P112</t>
+          <t>DT_1C91</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -3736,43 +3522,45 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>통계청</t>
-        </is>
-      </c>
-      <c r="E77" t="n">
-        <v>40.54</v>
-      </c>
-      <c r="F77" t="inlineStr"/>
+          <t>국가데이터처(지역소득)</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1C91</t>
+        </is>
+      </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>값 확인됨(자동 API 검증)</t>
+          <t>표 후보 확인 (주기 불일치)</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>API 실측(상위10대/계 비율계산) 2025Q3=40.54%(기사 40.0%), 2024Q3=37.38%(기사 37.4%). slots: period=202503/202403,flow=수출,rank_group=상위10대 vs 계</t>
+          <t>경북1.6%/울산1.4%/서울1.0% - 상동 이유로 분기 데이터 확인 안됨</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Claude(Claude Code, KOSIS API 실측 검증)</t>
+          <t>Claude(코시스 커넥터 자동 매칭, 수치 미대조)</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A058-01</t>
+          <t>A039-03</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>DT_1B04005N</t>
+          <t>DT_1C91</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -3780,167 +3568,145 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>국가데이터처(주민등록인구)</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>20-24세 2,647,814명 + 25-29세 3,307,842명 = 5,955,656명 (2024년, objL1=00 전국)</t>
-        </is>
-      </c>
+          <t>국가데이터처(지역소득)</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
-          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1B04005N</t>
+          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1C91</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>값 확인됨 (근접, 불일치)</t>
+          <t>표 후보 확인 (주기 불일치)</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>API 5세 단위 연령대(20-24/25-29) 합산 5,955,656명 vs 기사 630만2000명 — 차이 약 34만6000명(5.5%). 연령 구간 정의(20~29세 vs 20대) 또는 통계 기준일 차이로 추정.</t>
+          <t>건설업 GRDP -12.4%(분기) - 상동</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Claude(data_set.csv 키워드 필터링 + KOSIS 커넥터 API 검증, keyword_search 버전 비교 실험용 커버리지 보강)</t>
+          <t>Claude(코시스 커넥터 자동 매칭, 수치 미대조)</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A058-02</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>DT_1B04005N</t>
-        </is>
-      </c>
-      <c r="C79" t="n">
-        <v>101</v>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>국가데이터처(주민등록인구)</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>70-74~100+ 7개 구간 합산 6,629,643명 (2024년, objL1=00 전국)</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1B04005N</t>
-        </is>
-      </c>
+          <t>A040-01</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr"/>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>값 확인됨 (근접, 불일치)</t>
+          <t>매칭 실패</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>API 합산 6,629,643명 vs 기사 654만3000명 — 차이 약 8만6000명(1.3%), 근접.</t>
+          <t>청년층 '쉬었음' 인구(50.4만명) - 경제활동인구조사 내 '활동상태별 비경제활동인구'(쉬었음/가사/심신장애 등) 세부표를 로컬 카탈로그에서 찾지 못함, 별도 특수 분류표로 추정</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Claude(data_set.csv 키워드 필터링 + KOSIS 커넥터 API 검증, keyword_search 버전 비교 실험용 커버리지 보강)</t>
+          <t>Claude(코시스 커넥터 검색, 매칭 실패)</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A059-01</t>
+          <t>A040-02</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>DT_200Y102</t>
+          <t>DT_1DA7002S</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>301</v>
+        <v>101</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>한국은행(국민계정, 분기지표)</t>
+          <t>국가데이터처(경제활동인구조사)</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2024년 4분기 실질GDP 전기비(계절조정) = 0.2%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>https://kosis.kr/statHtml/statHtml.do?orgId=301&amp;tblId=DT_200Y102</t>
+          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1DA7002S</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>값 확인됨 (불일치)</t>
+          <t>값 확인됨 (일치)</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>기사(속보치, 2025-01-23 발표) 0.1% vs API(현재 게시된 개정치) 0.2% — GDP 속보치가 이후 잠정치로 개정된 사례로 추정.</t>
+          <t>연령별 경제활동인구총괄, 15-29세 2025.2 고용률=44.3%. 기사 수치와 일치</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Claude(data_set.csv 키워드 필터링 + KOSIS 커넥터 API 검증, keyword_search 버전 비교 실험용 커버리지 보강)</t>
+          <t>Claude(코시스 API 직접 조회, 수치 확인)</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A060-01</t>
+          <t>A040-03</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>DT_1R11006_FRM101</t>
+          <t>DT_1DA7002S</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>360</v>
+        <v>101</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>관세청(국가별 수출입)</t>
+          <t>국가데이터처(경제활동인구조사)</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2024년 전체 수출액 683,609,488천달러 ≈ 6836.1억달러</t>
+          <t>3,557,200명</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>https://kosis.kr/statHtml/statHtml.do?orgId=360&amp;tblId=DT_1R11006_FRM101</t>
+          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1DA7002S</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3950,125 +3716,93 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>기사 6838억달러 vs API 6836.1억달러 — 반올림 수준의 근사 일치.</t>
+          <t>15-29세 2025.2 취업자=3,557.2천명. 기사 수치(3,557,000명)와 사실상 일치(반올림 차이)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Claude(data_set.csv 키워드 필터링 + KOSIS 커넥터 API 검증, keyword_search 버전 비교 실험용 커버리지 보강)</t>
+          <t>Claude(코시스 API 직접 조회, 수치 확인)</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A061-01</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>DT_343_2010_S0027</t>
-        </is>
-      </c>
-      <c r="C82" t="n">
-        <v>343</v>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>한국거래소(코스피 지수)</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>2025년 3월 월말종가(연월말) = 2481.12</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>https://kosis.kr/statHtml/statHtml.do?orgId=343&amp;tblId=DT_343_2010_S0027</t>
-        </is>
-      </c>
+          <t>A041-01</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr"/>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>값 확인됨 (근접, 불일치)</t>
+          <t>매칭 실패</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>기사 2557.98(3/31 시작값으로 인용) vs API 월말종가 2481.12 — 차이 약 3%. 표는 월말 스냅샷만 제공해 특정일(3/31) 값과 정확히 일치하지 않을 수 있음.</t>
+          <t>가계금융복지조사 은퇴가구 최소/적정 생활비(원 단위) - '노후준비' 관련 검색 결과 모두 민간·타부처 패널조사(장애인삶패널, 다문화가족실태조사 등)만 나오고 통계청 가계금융복지조사 내 해당 항목 표는 찾지 못함</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Claude(data_set.csv 키워드 필터링 + KOSIS 커넥터 API 검증, keyword_search 버전 비교 실험용 커버리지 보강)</t>
+          <t>Claude(코시스 커넥터 검색, 매칭 실패)</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A062-01</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>DT_311Y001</t>
-        </is>
-      </c>
-      <c r="C83" t="n">
-        <v>301</v>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>한국은행(국제투자대조표)</t>
-        </is>
-      </c>
+          <t>A041-02</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr"/>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>https://kosis.kr/statHtml/statHtml.do?orgId=301&amp;tblId=DT_311Y001</t>
-        </is>
-      </c>
+      <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>표 후보 확인 (세부 코드 미확인)</t>
+          <t>매칭 실패</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>표 자체(대외금융자산 총계)는 API 검증됐으나, 기사가 인용한 하위 항목인 '증권투자'의 objL1 세부 코드가 아직 table_params.json에 없어 이번 라운드에선 수치 대조를 못함. objL1=ALL 스캔으로 코드 확인 필요.</t>
+          <t>생활비 여유/부족 응답비율 - 상동</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Claude(data_set.csv 키워드 필터링 + KOSIS 커넥터 API 검증, keyword_search 버전 비교 실험용 커버리지 보강)</t>
+          <t>Claude(코시스 커넥터 검색, 매칭 실패)</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A063-01</t>
+          <t>A042-01</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>DT_1JH20202</t>
+          <t>DT_1K41013</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -4076,113 +3810,113 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>국가데이터처(전산업생산지수)</t>
+          <t>국가데이터처(서비스업동향조사)</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
-          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1JH20202</t>
+          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1K41013</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>표 후보 확인 (증감률 계산 필요)</t>
+          <t>표 후보 확인 (총계 항목 미확인)</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>이 표는 지수 수준(2020=100)만 제공 — 기사의 '전월 대비 1.0% 증가'를 확인하려면 2025년 8월/9월 두 시점 지수를 조회해 계산해야 함(calculator.py 영역, 이번엔 미수행).</t>
+          <t>A022-01과 동일 수치(2024년 연간 소매판매 -2.2%), 동일 표·동일 사유</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Claude(data_set.csv 키워드 필터링 + KOSIS 커넥터 API 검증, keyword_search 버전 비교 실험용 커버리지 보강)</t>
+          <t>Claude(코시스 커넥터 자동 매칭, 수치 미대조)</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A064-01</t>
+          <t>A042-02</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>DT_115_2009_H3001_18_1</t>
+          <t>DT_1JH20201</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>산업통상자원부(외국인투자)</t>
+          <t>국가데이터처(전산업생산지수)</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2025년 1분기 신고금액 6,399,054천달러 ≈ 63.99억달러</t>
+          <t>113.5(2024)/111.7(2023)/+1.6%</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>https://kosis.kr/statHtml/statHtml.do?orgId=115&amp;tblId=DT_115_2009_H3001_18_1</t>
+          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1JH20201</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>값 확인됨 (일치)</t>
+          <t>값 확인됨 (근접, 불일치)</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>기사 64억1000만달러 vs API 63억9900만달러 — 근사 일치(0.2% 이내).</t>
+          <t>전산업생산지수(원지수, 농림어업포함) 2024=113.5, 2023=111.7 대비 +1.61%. 기사 수치(+1.7%)와 0.1%p 차이 - 근접하나 정확히 일치하지 않음 (농림어업 제외 기준도 동일하게 +1.6%)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Claude(data_set.csv 키워드 필터링 + KOSIS 커넥터 API 검증, keyword_search 버전 비교 실험용 커버리지 보강)</t>
+          <t>Claude(코시스 API 직접 조회, 수치 확인)</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A065-01</t>
+          <t>A042-03</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>DT_301Y013</t>
+          <t>DT_1G18011</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>301</v>
+        <v>101</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>한국은행(국제수지)</t>
+          <t>국가데이터처(건설경기동향조사)</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2024년 경상수지 99,973.5백만달러 ≈ 999.7억달러</t>
+          <t>136,209,903백만원/-4.6%</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>https://kosis.kr/statHtml/statHtml.do?orgId=301&amp;tblId=DT_301Y013</t>
+          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1G18011</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -4192,213 +3926,17 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>기사 990억4000만달러 vs API 999억7350만달러 — 차이 약 0.9%, 속보치/확정치 개정 추정.</t>
+          <t>건설기성액(불변) 2024=136,209,903백만원, 2023(142,775,612백만원) 대비 -4.60%. 기사 수치(-4.9%)와 0.3%p 차이 - 근접하나 정확히 일치하지 않음</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Claude(data_set.csv 키워드 필터링 + KOSIS 커넥터 API 검증, keyword_search 버전 비교 실험용 커버리지 보강)</t>
+          <t>Claude(코시스 API 직접 조회, 수치 확인)</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>A066-01</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>DT_1F70011</t>
-        </is>
-      </c>
-      <c r="C87" t="n">
-        <v>101</v>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>국가데이터처(설비투자지수)</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>계절조정지수 2024-12=124.0 → 2025-01=105.5 (전월비 -14.9%)</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1F70011</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>값 확인됨 (근접, 불일치)</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>기사 -14.2% vs API 계산 -14.9% — 차이 0.7%p, 지수 반올림/개정 차이로 추정.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>Claude(data_set.csv 키워드 필터링 + KOSIS 커넥터 API 검증, keyword_search 버전 비교 실험용 커버리지 보강)</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>A067-01</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>DT_404Y014</t>
-        </is>
-      </c>
-      <c r="C88" t="n">
-        <v>301</v>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>한국은행(생산자물가지수)</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>총지수 2025-03=120.36 → 2025-04=120.14 (전월비 -0.18%)</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>https://kosis.kr/statHtml/statHtml.do?orgId=301&amp;tblId=DT_404Y014</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>값 확인됨 (근접, 일치)</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>기사 -0.1% vs API 계산 -0.18% — 지수 반올림에 따른 재계산 오차, 방향/규모 일치.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>Claude(data_set.csv 키워드 필터링 + KOSIS 커넥터 API 검증, keyword_search 버전 비교 실험용 커버리지 보강)</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>A068-01</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>DT_IMEMIB001</t>
-        </is>
-      </c>
-      <c r="C89" t="n">
-        <v>101</v>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>국가데이터처(소득이동통계)</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_IMEMIB001</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>표 후보 확인 (비율 계산 필요)</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>기사의 '한 계단 이상 상승 17.3%'는 전년도 분위별 당해연도 2~5분위 이동자를 합산해야 하는 파생 지표라 단일 조회로는 안 나옴 — itmId 여러 개 합산 필요(미계산).</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>Claude(data_set.csv 키워드 필터링 + KOSIS 커넥터 API 검증, keyword_search 버전 비교 실험용 커버리지 보강)</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>A069-01</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>DT_200Y001</t>
-        </is>
-      </c>
-      <c r="C90" t="n">
-        <v>301</v>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>한국은행(주요지표 연간지표)</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>2023년 1인당 GNI(달러표시) 33,745달러만 API에 존재, 2024년치 미발표(err30)</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>https://kosis.kr/statHtml/statHtml.do?orgId=301&amp;tblId=DT_200Y001</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>표 후보 확인 (최신년도 미제공)</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>기사(2025-06)는 2024년치 3만6745달러를 인용하나, 이 KOSIS 표는 조회 시점(2026-07-31) 기준 2023년까지만 게시되어 있어 직접 대조 불가.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>Claude(data_set.csv 키워드 필터링 + KOSIS 커넥터 API 검증, keyword_search 버전 비교 실험용 커버리지 보강)</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
